--- a/多平台商品上架字段总表_马洁填写版.xlsx
+++ b/多平台商品上架字段总表_马洁填写版.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2111" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="1018">
   <si>
     <t xml:space="preserve">多平台商品上架字段总表 · 填写说明</t>
   </si>
@@ -310,18 +310,30 @@
     <t xml:space="preserve">与执照完全一致，一个字都不能差</t>
   </si>
   <si>
+    <t xml:space="preserve">天津市西青区聚鸿津豪汽车配件销售店（个体工商户）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">执照注册日 2016-12-14，2026-04-21 换发；经营范围仅「汽车配件、汽车用品批发兼零售」</t>
+  </si>
+  <si>
     <t xml:space="preserve">统一社会信用代码</t>
   </si>
   <si>
     <t xml:space="preserve">18 位</t>
   </si>
   <si>
+    <t xml:space="preserve">92120103MA05M2BM7T</t>
+  </si>
+  <si>
     <t xml:space="preserve">主体类型</t>
   </si>
   <si>
     <t xml:space="preserve">个体工商户 / 有限公司</t>
   </si>
   <si>
+    <t xml:space="preserve">个体工商户（个人经营）</t>
+  </si>
+  <si>
     <t xml:space="preserve">个体工商户在部分高风险类目会受限</t>
   </si>
   <si>
@@ -331,25 +343,37 @@
     <t xml:space="preserve">与执照一致</t>
   </si>
   <si>
+    <t xml:space="preserve">个体户执照上称「经营者」，与法人同一栏</t>
+  </si>
+  <si>
     <t xml:space="preserve">法人手机号</t>
   </si>
   <si>
     <t xml:space="preserve">能接收验证码、能接审核电话</t>
   </si>
   <si>
+    <t xml:space="preserve">13820908557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">取原表「老板手机」预填，请确认是马洁本人实名号</t>
+  </si>
+  <si>
     <t xml:space="preserve">执照注册地址</t>
   </si>
   <si>
     <t xml:space="preserve">与执照完全一致</t>
   </si>
   <si>
+    <t xml:space="preserve">天津市西青区大寺镇梅江灯饰广场南侧20米院内展厅114及连接维修车间</t>
+  </si>
+  <si>
     <t xml:space="preserve">实际经营地址</t>
   </si>
   <si>
     <t xml:space="preserve">写到门牌号/楼层，便于审核比对</t>
   </si>
   <si>
-    <t xml:space="preserve">与执照不一致时，备好一句解释口径</t>
+    <t xml:space="preserve">按执照地址填；若实际门店与执照不同，需备一句解释口径</t>
   </si>
   <si>
     <t xml:space="preserve">地图定位名称（POI）</t>
@@ -358,6 +382,9 @@
     <t xml:space="preserve">地图上能搜到的名称；搜不到就先新建</t>
   </si>
   <si>
+    <t xml:space="preserve">待确认：与门头招牌保持一致，先在地图搜「聚鸿津豪汽车配件销售店」</t>
+  </si>
+  <si>
     <t xml:space="preserve">抖音 快手 小红书 美团 点评</t>
   </si>
   <si>
@@ -391,9 +418,6 @@
     <t xml:space="preserve">老板手机</t>
   </si>
   <si>
-    <t xml:space="preserve">13820908557</t>
-  </si>
-  <si>
     <t xml:space="preserve">微信号/私信口径</t>
   </si>
   <si>
@@ -430,7 +454,10 @@
     <t xml:space="preserve">汽车服务 &gt; 汽车美容/贴膜；美团为 爱车 &gt; 美容</t>
   </si>
   <si>
-    <t xml:space="preserve">类目填错，后面流量全偏</t>
+    <t xml:space="preserve">汽车服务 &gt; 汽车美容/贴膜（美团为：爱车 &gt; 汽车美容）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️ 执照经营范围未含「汽车美容/贴膜服务」，美团/抖音类目审核可能要求补充；建议到西青区市场监管增项「汽车美容服务、机动车维修」，否则贴膜类目有被驳回风险</t>
   </si>
   <si>
     <t xml:space="preserve">门店简介（短·50字）</t>
@@ -439,15 +466,27 @@
     <t xml:space="preserve">做什么 + 做了多久 + 一句信任点</t>
   </si>
   <si>
+    <t xml:space="preserve">【草稿】西青大寺 2016 年开店，专做隐形车衣、玻璃膜、改色膜，一线师傅施工。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI 拟稿，请按实际改写后再用</t>
+  </si>
+  <si>
     <t xml:space="preserve">门店简介（长·200字）</t>
   </si>
   <si>
     <t xml:space="preserve">适合美团/大众点评商户介绍</t>
   </si>
   <si>
+    <t xml:space="preserve">【草稿】津豪汽车贴膜改装，2016 年开业，位于西青区大寺镇梅江灯饰广场南侧，自有施工车间。主营隐形车衣、改色膜、玻璃隔热膜与内饰改装，专车专用裁膜，膜材品牌与型号可查；施工前验车拍照留档，质保卡编号可追溯。贴膜、改色、内饰可一处完成，支持预约到店。</t>
+  </si>
+  <si>
     <t xml:space="preserve">美团 点评 小红书</t>
   </si>
   <si>
+    <t xml:space="preserve">AI 拟稿，请按实际改写后再用；平台允许时可再扩到 200 字</t>
+  </si>
+  <si>
     <t xml:space="preserve">工位/施工车间数量</t>
   </si>
   <si>
@@ -469,6 +508,9 @@
     <t xml:space="preserve">轿车/SUV/MPV/新能源；是否接超跑、改装车</t>
   </si>
   <si>
+    <t xml:space="preserve">轿车 / SUV / MPV / 新能源；超跑、改装车是否接待待确认</t>
+  </si>
+  <si>
     <t xml:space="preserve">交通与停车指引</t>
   </si>
   <si>
@@ -487,6 +529,12 @@
     <t xml:space="preserve">清晰、四角完整、不反光</t>
   </si>
   <si>
+    <t xml:space="preserve">已有：2026-04-21 换发版，可用于平台认证</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机翻拍件；上传前按「四角完整、不反光、JPG」重拍</t>
+  </si>
+  <si>
     <t xml:space="preserve">法人身份证正反面</t>
   </si>
   <si>
@@ -517,7 +565,13 @@
     <t xml:space="preserve">贴膜一般不需要；改内饰/改装按当地要求</t>
   </si>
   <si>
+    <t xml:space="preserve">本店执照经营范围未含贴膜/美容服务，类目审核有风险（见备注）</t>
+  </si>
+  <si>
     <t xml:space="preserve">按类目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">与「门店类目」备注是同一件事：需先做经营范围增项</t>
   </si>
   <si>
     <t xml:space="preserve">门头照</t>
@@ -4556,7 +4610,7 @@
       </c>
       <c r="G5" s="14"/>
     </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
         <v>84</v>
       </c>
@@ -4569,26 +4623,32 @@
       <c r="D6" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="16" t="s">
+        <v>91</v>
+      </c>
       <c r="F6" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G6" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="16"/>
+        <v>94</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>95</v>
+      </c>
       <c r="F7" s="24" t="s">
         <v>88</v>
       </c>
@@ -4599,119 +4659,135 @@
         <v>84</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="16"/>
+        <v>97</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>98</v>
+      </c>
       <c r="F8" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>7</v>
+      </c>
       <c r="F9" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G9" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="16"/>
+        <v>104</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>105</v>
+      </c>
       <c r="F10" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G10" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>109</v>
+      </c>
       <c r="F11" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G11" s="14"/>
     </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="16"/>
+        <v>111</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>109</v>
+      </c>
       <c r="F12" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
         <v>84</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="16"/>
+        <v>114</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>115</v>
+      </c>
       <c r="F13" s="24" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4719,13 +4795,13 @@
         <v>84</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="24" t="s">
@@ -4735,7 +4811,7 @@
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="23"/>
@@ -4746,19 +4822,19 @@
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F16" s="24" t="s">
         <v>88</v>
@@ -4767,19 +4843,19 @@
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F17" s="24" t="s">
         <v>88</v>
@@ -4788,28 +4864,28 @@
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>110</v>
-      </c>
       <c r="D18" s="14" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B19" s="23"/>
       <c r="C19" s="23"/>
@@ -4820,19 +4896,19 @@
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>88</v>
@@ -4841,136 +4917,148 @@
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C22" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" s="16"/>
+        <v>138</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>139</v>
+      </c>
       <c r="F22" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="16"/>
+        <v>142</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>143</v>
+      </c>
       <c r="F23" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G23" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="123" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" s="16"/>
+        <v>146</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>147</v>
+      </c>
       <c r="F24" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="G24" s="14"/>
+        <v>148</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="24" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="E26" s="16"/>
       <c r="F26" s="24" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G26" s="14"/>
     </row>
-    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="E27" s="16"/>
+        <v>156</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>157</v>
+      </c>
       <c r="F27" s="24" t="s">
         <v>88</v>
       </c>
@@ -4978,28 +5066,28 @@
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="24" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
@@ -5008,37 +5096,41 @@
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
     </row>
-    <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" s="16"/>
+        <v>163</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>164</v>
+      </c>
       <c r="F30" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G30" s="14"/>
+      <c r="G30" s="14" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E31" s="16"/>
       <c r="F31" s="24" t="s">
@@ -5048,94 +5140,98 @@
     </row>
     <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E32" s="16"/>
       <c r="F32" s="24" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G32" s="14"/>
     </row>
     <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="E33" s="16"/>
       <c r="F33" s="24" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="G33" s="14"/>
     </row>
-    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="16"/>
+        <v>175</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>176</v>
+      </c>
       <c r="F34" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="G34" s="14"/>
+        <v>177</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="E36" s="16"/>
       <c r="F36" s="24" t="s">
@@ -5145,7 +5241,7 @@
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
@@ -5156,16 +5252,16 @@
     </row>
     <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="24" t="s">
@@ -5175,47 +5271,47 @@
     </row>
     <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C39" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="E39" s="16"/>
       <c r="F39" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="E40" s="16"/>
       <c r="F40" s="24" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="G40" s="14"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -5226,16 +5322,16 @@
     </row>
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C42" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E42" s="16"/>
       <c r="F42" s="24" t="s">
@@ -5245,58 +5341,58 @@
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="C43" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="E43" s="16"/>
       <c r="F43" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="E44" s="16"/>
       <c r="F44" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C45" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="E45" s="16"/>
       <c r="F45" s="24" t="s">
@@ -5306,37 +5402,37 @@
     </row>
     <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="C46" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E46" s="16"/>
       <c r="F46" s="24" t="s">
         <v>88</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C47" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E47" s="16"/>
       <c r="F47" s="24" t="s">
@@ -5346,16 +5442,16 @@
     </row>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C48" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E48" s="16"/>
       <c r="F48" s="24" t="s">
@@ -5365,26 +5461,26 @@
     </row>
     <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="C49" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="E49" s="16"/>
       <c r="F49" s="24" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B50" s="23"/>
       <c r="C50" s="23"/>
@@ -5395,35 +5491,35 @@
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E51" s="16"/>
       <c r="F51" s="24" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="G51" s="14"/>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="E52" s="16"/>
       <c r="F52" s="24" t="s">
@@ -5433,35 +5529,35 @@
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="E53" s="16"/>
       <c r="F53" s="24" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="G53" s="14"/>
     </row>
     <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E54" s="16"/>
       <c r="F54" s="24" t="s">
@@ -5471,16 +5567,16 @@
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="E55" s="16"/>
       <c r="F55" s="24" t="s">
@@ -5531,7 +5627,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5546,7 +5642,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5573,22 +5669,22 @@
         <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>83</v>
@@ -5596,7 +5692,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
@@ -5611,16 +5707,16 @@
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="27"/>
@@ -5632,13 +5728,13 @@
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>88</v>
@@ -5653,16 +5749,16 @@
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>216</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>198</v>
       </c>
       <c r="E7" s="27"/>
       <c r="F7" s="27"/>
@@ -5674,16 +5770,16 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E8" s="27"/>
       <c r="F8" s="27"/>
@@ -5695,13 +5791,13 @@
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>72</v>
@@ -5716,13 +5812,13 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>74</v>
@@ -5737,16 +5833,16 @@
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E11" s="27"/>
       <c r="F11" s="27"/>
@@ -5758,13 +5854,13 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>88</v>
@@ -5779,13 +5875,13 @@
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D13" s="26" t="s">
         <v>88</v>
@@ -5800,13 +5896,13 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>88</v>
@@ -5821,16 +5917,16 @@
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="E15" s="27"/>
       <c r="F15" s="27"/>
@@ -5842,16 +5938,16 @@
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
@@ -5863,13 +5959,13 @@
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>88</v>
@@ -5884,13 +5980,13 @@
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>88</v>
@@ -5905,13 +6001,13 @@
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>88</v>
@@ -5926,7 +6022,7 @@
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -5941,13 +6037,13 @@
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="D21" s="26" t="s">
         <v>88</v>
@@ -5962,13 +6058,13 @@
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>88</v>
@@ -5983,16 +6079,16 @@
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
@@ -6004,16 +6100,16 @@
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
@@ -6025,16 +6121,16 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E25" s="27"/>
       <c r="F25" s="27"/>
@@ -6046,16 +6142,16 @@
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
@@ -6067,16 +6163,16 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
@@ -6088,16 +6184,16 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E28" s="27"/>
       <c r="F28" s="27"/>
@@ -6109,16 +6205,16 @@
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="E29" s="27"/>
       <c r="F29" s="27"/>
@@ -6130,16 +6226,16 @@
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="E30" s="27"/>
       <c r="F30" s="27"/>
@@ -6151,16 +6247,16 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E31" s="29"/>
       <c r="F31" s="29"/>
@@ -6172,16 +6268,16 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E32" s="29"/>
       <c r="F32" s="29"/>
@@ -6193,16 +6289,16 @@
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E33" s="29"/>
       <c r="F33" s="29"/>
@@ -6214,13 +6310,13 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>55</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D34" s="26" t="s">
         <v>88</v>
@@ -6235,13 +6331,13 @@
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="D35" s="26" t="s">
         <v>88</v>
@@ -6256,16 +6352,16 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="E36" s="27"/>
       <c r="F36" s="27"/>
@@ -6277,16 +6373,16 @@
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E37" s="27"/>
       <c r="F37" s="27"/>
@@ -6298,13 +6394,13 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D38" s="26" t="s">
         <v>88</v>
@@ -6319,16 +6415,16 @@
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E39" s="29"/>
       <c r="F39" s="29"/>
@@ -6340,7 +6436,7 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -6355,13 +6451,13 @@
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>53</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="D41" s="26" t="s">
         <v>88</v>
@@ -6376,13 +6472,13 @@
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D42" s="26" t="s">
         <v>88</v>
@@ -6397,16 +6493,16 @@
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="E43" s="31"/>
       <c r="F43" s="31"/>
@@ -6418,16 +6514,16 @@
     </row>
     <row r="44" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="E44" s="33" t="str">
         <f aca="false">IF(E42="","",ROUND(E42*0.94,2))</f>
@@ -6457,16 +6553,16 @@
     </row>
     <row r="45" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="E45" s="33" t="str">
         <f aca="false">IF(OR(E44="",E43=""),"",ROUND(E44-E43,2))</f>
@@ -6496,16 +6592,16 @@
     </row>
     <row r="46" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="E46" s="34" t="str">
         <f aca="false">IF(OR(E44="",E44=0,E45=""),"",E45/E44)</f>
@@ -6535,13 +6631,13 @@
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D47" s="26" t="s">
         <v>88</v>
@@ -6556,16 +6652,16 @@
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E48" s="29"/>
       <c r="F48" s="29"/>
@@ -6577,13 +6673,13 @@
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="D49" s="26" t="s">
         <v>88</v>
@@ -6598,13 +6694,13 @@
     </row>
     <row r="50" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="D50" s="26" t="s">
         <v>88</v>
@@ -6619,16 +6715,16 @@
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E51" s="27"/>
       <c r="F51" s="27"/>
@@ -6640,7 +6736,7 @@
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B52" s="23"/>
       <c r="C52" s="23"/>
@@ -6655,13 +6751,13 @@
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="D53" s="26" t="s">
         <v>88</v>
@@ -6676,13 +6772,13 @@
     </row>
     <row r="54" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="D54" s="26" t="s">
         <v>88</v>
@@ -6697,13 +6793,13 @@
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="D55" s="26" t="s">
         <v>88</v>
@@ -6718,13 +6814,13 @@
     </row>
     <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="D56" s="26" t="s">
         <v>88</v>
@@ -6739,13 +6835,13 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="D57" s="26" t="s">
         <v>88</v>
@@ -6760,16 +6856,16 @@
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E58" s="27"/>
       <c r="F58" s="27"/>
@@ -6781,13 +6877,13 @@
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="D59" s="26" t="s">
         <v>88</v>
@@ -6802,16 +6898,16 @@
     </row>
     <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="27"/>
@@ -6823,16 +6919,16 @@
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="E61" s="27"/>
       <c r="F61" s="27"/>
@@ -6844,16 +6940,16 @@
     </row>
     <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E62" s="27"/>
       <c r="F62" s="27"/>
@@ -6865,16 +6961,16 @@
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E63" s="27"/>
       <c r="F63" s="27"/>
@@ -6886,13 +6982,13 @@
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="D64" s="26" t="s">
         <v>88</v>
@@ -6907,7 +7003,7 @@
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="23" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B65" s="23"/>
       <c r="C65" s="23"/>
@@ -6922,13 +7018,13 @@
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="D66" s="26" t="s">
         <v>88</v>
@@ -6943,13 +7039,13 @@
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="D67" s="26" t="s">
         <v>88</v>
@@ -6964,13 +7060,13 @@
     </row>
     <row r="68" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="D68" s="26" t="s">
         <v>88</v>
@@ -6985,13 +7081,13 @@
     </row>
     <row r="69" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D69" s="26" t="s">
         <v>88</v>
@@ -7006,13 +7102,13 @@
     </row>
     <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D70" s="26" t="s">
         <v>88</v>
@@ -7027,16 +7123,16 @@
     </row>
     <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="E71" s="27"/>
       <c r="F71" s="27"/>
@@ -7048,16 +7144,16 @@
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="E72" s="27"/>
       <c r="F72" s="27"/>
@@ -7069,7 +7165,7 @@
     </row>
     <row r="73" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B73" s="23"/>
       <c r="C73" s="23"/>
@@ -7084,13 +7180,13 @@
     </row>
     <row r="74" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="D74" s="26" t="s">
         <v>88</v>
@@ -7105,13 +7201,13 @@
     </row>
     <row r="75" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="D75" s="26" t="s">
         <v>88</v>
@@ -7126,13 +7222,13 @@
     </row>
     <row r="76" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="D76" s="26" t="s">
         <v>88</v>
@@ -7147,13 +7243,13 @@
     </row>
     <row r="77" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="D77" s="26" t="s">
         <v>88</v>
@@ -7168,16 +7264,16 @@
     </row>
     <row r="78" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="E78" s="27"/>
       <c r="F78" s="27"/>
@@ -7189,16 +7285,16 @@
     </row>
     <row r="79" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="E79" s="27"/>
       <c r="F79" s="27"/>
@@ -7210,16 +7306,16 @@
     </row>
     <row r="80" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D80" s="26" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E80" s="27"/>
       <c r="F80" s="27"/>
@@ -7231,13 +7327,13 @@
     </row>
     <row r="81" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D81" s="26" t="s">
         <v>69</v>
@@ -7252,13 +7348,13 @@
     </row>
     <row r="82" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="D82" s="26" t="s">
         <v>69</v>
@@ -7273,16 +7369,16 @@
     </row>
     <row r="83" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="E83" s="27"/>
       <c r="F83" s="27"/>
@@ -7294,16 +7390,16 @@
     </row>
     <row r="84" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="D84" s="26" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="E84" s="27"/>
       <c r="F84" s="27"/>
@@ -7315,7 +7411,7 @@
     </row>
     <row r="85" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="23" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B85" s="23"/>
       <c r="C85" s="23"/>
@@ -7330,13 +7426,13 @@
     </row>
     <row r="86" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="D86" s="26" t="s">
         <v>88</v>
@@ -7351,13 +7447,13 @@
     </row>
     <row r="87" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="D87" s="26" t="s">
         <v>88</v>
@@ -7372,13 +7468,13 @@
     </row>
     <row r="88" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="D88" s="26" t="s">
         <v>88</v>
@@ -7393,13 +7489,13 @@
     </row>
     <row r="89" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="D89" s="26" t="s">
         <v>88</v>
@@ -7414,13 +7510,13 @@
     </row>
     <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="D90" s="26" t="s">
         <v>88</v>
@@ -7474,7 +7570,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7487,7 +7583,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7506,13 +7602,13 @@
         <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>69</v>
@@ -7524,12 +7620,12 @@
         <v>74</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
@@ -7542,10 +7638,10 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>79</v>
@@ -7566,18 +7662,18 @@
         <v>79</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D6" s="38" t="s">
         <v>79</v>
@@ -7586,7 +7682,7 @@
         <v>79</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>79</v>
@@ -7595,15 +7691,15 @@
         <v>79</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>79</v>
@@ -7615,24 +7711,24 @@
         <v>79</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>79</v>
@@ -7653,12 +7749,12 @@
         <v>79</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
@@ -7671,10 +7767,10 @@
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>79</v>
@@ -7695,56 +7791,56 @@
         <v>79</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E11" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E12" s="38" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>79</v>
@@ -7753,12 +7849,12 @@
         <v>79</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -7771,10 +7867,10 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>79</v>
@@ -7789,21 +7885,21 @@
         <v>79</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H14" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C15" s="38" t="s">
         <v>79</v>
@@ -7824,27 +7920,27 @@
         <v>79</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>79</v>
@@ -7853,19 +7949,19 @@
         <v>79</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>427</v>
+      </c>
+      <c r="C17" s="38" t="s">
         <v>416</v>
       </c>
-      <c r="B17" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>398</v>
-      </c>
       <c r="D17" s="38" t="s">
         <v>79</v>
       </c>
@@ -7873,21 +7969,21 @@
         <v>79</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B18" s="23"/>
       <c r="C18" s="23"/>
@@ -7900,263 +7996,263 @@
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E19" s="38" t="s">
         <v>79</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H19" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H20" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E21" s="38" t="s">
         <v>79</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H21" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C23" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H23" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C24" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H25" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C26" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H26" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C27" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H27" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8164,149 +8260,149 @@
         <v>55</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H28" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C29" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H29" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C30" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E30" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H30" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C31" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E31" s="38" t="s">
         <v>79</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E32" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H32" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -8319,36 +8415,36 @@
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="E34" s="38" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="F34" s="38" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="G34" s="38" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
@@ -8361,10 +8457,10 @@
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C36" s="38" t="s">
         <v>79</v>
@@ -8379,18 +8475,18 @@
         <v>79</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="H36" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I36" s="26" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
@@ -8403,10 +8499,10 @@
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C38" s="38" t="s">
         <v>79</v>
@@ -8421,21 +8517,21 @@
         <v>79</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H38" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>79</v>
@@ -8450,21 +8546,21 @@
         <v>79</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>79</v>
@@ -8479,50 +8575,50 @@
         <v>79</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H40" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C41" s="38" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C42" s="38" t="s">
         <v>79</v>
@@ -8537,24 +8633,24 @@
         <v>79</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I42" s="26" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="D43" s="38" t="s">
         <v>79</v>
@@ -8566,21 +8662,21 @@
         <v>79</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="H43" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C44" s="38" t="s">
         <v>79</v>
@@ -8592,21 +8688,21 @@
         <v>79</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G44" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H44" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B45" s="23"/>
       <c r="C45" s="23"/>
@@ -8619,13 +8715,13 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D46" s="38" t="s">
         <v>79</v>
@@ -8637,18 +8733,18 @@
         <v>79</v>
       </c>
       <c r="G46" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="B47" s="23"/>
       <c r="C47" s="23"/>
@@ -8661,65 +8757,65 @@
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G48" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I48" s="26" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B49" s="37" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D49" s="38" t="s">
         <v>79</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H49" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I49" s="26" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="B50" s="23"/>
       <c r="C50" s="23"/>
@@ -8732,36 +8828,36 @@
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B51" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D51" s="38" t="s">
         <v>79</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G51" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I51" s="26" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B52" s="23"/>
       <c r="C52" s="23"/>
@@ -8774,22 +8870,22 @@
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E53" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F53" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G53" s="38" t="s">
         <v>79</v>
@@ -8798,12 +8894,12 @@
         <v>79</v>
       </c>
       <c r="I53" s="26" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
@@ -8816,36 +8912,36 @@
     </row>
     <row r="55" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G55" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H55" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I55" s="26" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B56" s="23"/>
       <c r="C56" s="23"/>
@@ -8858,36 +8954,36 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B57" s="37" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F57" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H57" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I57" s="26" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B58" s="23"/>
       <c r="C58" s="23"/>
@@ -8900,36 +8996,36 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="B59" s="37" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F59" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G59" s="38" t="s">
         <v>79</v>
       </c>
       <c r="H59" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I59" s="26" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B60" s="23"/>
       <c r="C60" s="23"/>
@@ -8942,36 +9038,36 @@
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="B61" s="37" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F61" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G61" s="38" t="s">
         <v>79</v>
       </c>
       <c r="H61" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="23" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="B62" s="23"/>
       <c r="C62" s="23"/>
@@ -8984,36 +9080,36 @@
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E63" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F63" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H63" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="23" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="B64" s="23"/>
       <c r="C64" s="23"/>
@@ -9026,100 +9122,100 @@
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="B65" s="37" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>79</v>
       </c>
       <c r="G65" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H65" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I65" s="26" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D66" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>79</v>
       </c>
       <c r="G66" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H66" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>79</v>
       </c>
       <c r="G67" s="38" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H67" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D68" s="38" t="s">
         <v>79</v>
@@ -9131,24 +9227,24 @@
         <v>79</v>
       </c>
       <c r="G68" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H68" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D69" s="38" t="s">
         <v>79</v>
@@ -9160,18 +9256,18 @@
         <v>79</v>
       </c>
       <c r="G69" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H69" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="23" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B70" s="23"/>
       <c r="C70" s="23"/>
@@ -9184,10 +9280,10 @@
     </row>
     <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="B71" s="37" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="C71" s="38" t="s">
         <v>79</v>
@@ -9202,21 +9298,21 @@
         <v>79</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="H71" s="38" t="s">
         <v>79</v>
       </c>
       <c r="I71" s="26" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="B72" s="37" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="C72" s="38" t="s">
         <v>79</v>
@@ -9231,13 +9327,13 @@
         <v>79</v>
       </c>
       <c r="G72" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="H72" s="38" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="I72" s="26" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -9308,7 +9404,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9318,7 +9414,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9328,7 +9424,7 @@
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -9338,7 +9434,7 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B4" s="40" t="s">
         <v>45</v>
@@ -9347,13 +9443,13 @@
         <v>79</v>
       </c>
       <c r="D4" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9361,19 +9457,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9381,19 +9477,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9401,19 +9497,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9421,19 +9517,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9441,19 +9537,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="C9" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9461,16 +9557,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F10" s="44"/>
     </row>
@@ -9479,19 +9575,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="C11" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9499,19 +9595,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="C12" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D12" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9519,19 +9615,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9539,16 +9635,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C14" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D14" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="F14" s="44"/>
     </row>
@@ -9557,19 +9653,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9577,19 +9673,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9597,16 +9693,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="F17" s="44"/>
     </row>
@@ -9615,16 +9711,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="F18" s="44"/>
     </row>
@@ -9633,16 +9729,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="E19" s="43" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="F19" s="44"/>
     </row>
@@ -9651,19 +9747,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E20" s="43" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9671,16 +9767,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="F21" s="44"/>
     </row>
@@ -9689,16 +9785,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D22" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E22" s="43" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="F22" s="44"/>
     </row>
@@ -9707,16 +9803,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="C23" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="E23" s="43" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F23" s="44"/>
     </row>
@@ -9725,19 +9821,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D24" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9745,19 +9841,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9765,19 +9861,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D26" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="F26" s="44" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9785,19 +9881,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9805,19 +9901,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="C28" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D28" s="42" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9825,19 +9921,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9845,19 +9941,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D30" s="42" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9871,10 +9967,10 @@
         <v>79</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E31" s="43" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="F31" s="44"/>
     </row>
@@ -9883,16 +9979,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C32" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D32" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E32" s="43" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="F32" s="44"/>
     </row>
@@ -9901,16 +9997,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="C33" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="E33" s="43" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="F33" s="44"/>
     </row>
@@ -9919,16 +10015,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D34" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E34" s="43" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="F34" s="44"/>
     </row>
@@ -9937,19 +10033,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C35" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="E35" s="43" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9957,16 +10053,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="C36" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D36" s="42" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="E36" s="43" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="F36" s="44"/>
     </row>
@@ -9975,16 +10071,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C37" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E37" s="43" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="F37" s="44"/>
     </row>
@@ -9993,16 +10089,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="C38" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D38" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E38" s="43" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="F38" s="44"/>
     </row>
@@ -10011,16 +10107,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="C39" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E39" s="43" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="F39" s="44"/>
     </row>
@@ -10029,16 +10125,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="C40" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D40" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E40" s="43" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="F40" s="44"/>
     </row>
@@ -10047,16 +10143,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C41" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E41" s="43" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F41" s="44"/>
     </row>
@@ -10065,25 +10161,25 @@
         <v>38</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C42" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D42" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E42" s="43" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="F42" s="44" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="39" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="B44" s="39"/>
       <c r="C44" s="39"/>
@@ -10093,7 +10189,7 @@
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B45" s="40" t="s">
         <v>45</v>
@@ -10102,13 +10198,13 @@
         <v>79</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10116,19 +10212,19 @@
         <v>1</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="C46" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D46" s="42" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
       <c r="E46" s="43" t="s">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F46" s="44" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10136,19 +10232,19 @@
         <v>2</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="C47" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E47" s="43" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10156,19 +10252,19 @@
         <v>3</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C48" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D48" s="42" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="E48" s="43" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="F48" s="44" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10182,10 +10278,10 @@
         <v>79</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E49" s="43" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="F49" s="44"/>
     </row>
@@ -10194,16 +10290,16 @@
         <v>5</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="C50" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D50" s="42" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="E50" s="43" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="F50" s="44"/>
     </row>
@@ -10212,19 +10308,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="C51" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="E51" s="43" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="F51" s="44" t="s">
-        <v>605</v>
+        <v>623</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10232,16 +10328,16 @@
         <v>7</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="C52" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D52" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E52" s="43" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="F52" s="44"/>
     </row>
@@ -10250,16 +10346,16 @@
         <v>8</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="C53" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="F53" s="44"/>
     </row>
@@ -10268,16 +10364,16 @@
         <v>9</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="F54" s="44"/>
     </row>
@@ -10286,16 +10382,16 @@
         <v>10</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C55" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="F55" s="44"/>
     </row>
@@ -10304,19 +10400,19 @@
         <v>11</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C56" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D56" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10324,16 +10420,16 @@
         <v>12</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="C57" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D57" s="42" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="F57" s="44"/>
     </row>
@@ -10342,16 +10438,16 @@
         <v>13</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="C58" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D58" s="42" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="E58" s="43" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
       <c r="F58" s="44"/>
     </row>
@@ -10360,16 +10456,16 @@
         <v>14</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="C59" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D59" s="42" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="E59" s="43" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="F59" s="44"/>
     </row>
@@ -10378,16 +10474,16 @@
         <v>15</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="C60" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D60" s="42" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="E60" s="43" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="F60" s="44"/>
     </row>
@@ -10396,19 +10492,19 @@
         <v>16</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="C61" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D61" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E61" s="43" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="F61" s="44" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10416,16 +10512,16 @@
         <v>17</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="C62" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D62" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E62" s="43" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="F62" s="44"/>
     </row>
@@ -10434,19 +10530,19 @@
         <v>18</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="C63" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D63" s="42" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="E63" s="43" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="F63" s="44" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10454,16 +10550,16 @@
         <v>19</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="C64" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D64" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E64" s="43" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F64" s="44"/>
     </row>
@@ -10472,19 +10568,19 @@
         <v>20</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="C65" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D65" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E65" s="43" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="F65" s="44" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10492,16 +10588,16 @@
         <v>21</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C66" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D66" s="42" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="E66" s="43" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="F66" s="44"/>
     </row>
@@ -10510,16 +10606,16 @@
         <v>22</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="C67" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D67" s="42" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="E67" s="43" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="F67" s="44"/>
     </row>
@@ -10528,16 +10624,16 @@
         <v>23</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>640</v>
+        <v>658</v>
       </c>
       <c r="C68" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D68" s="42" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="E68" s="43" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="F68" s="44"/>
     </row>
@@ -10554,7 +10650,7 @@
     </row>
     <row r="71" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B71" s="40" t="s">
         <v>45</v>
@@ -10563,13 +10659,13 @@
         <v>79</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E71" s="40" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F71" s="40" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10577,19 +10673,19 @@
         <v>1</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="C72" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D72" s="42" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
       <c r="E72" s="43" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="F72" s="44" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10597,16 +10693,16 @@
         <v>2</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="C73" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D73" s="42" t="s">
-        <v>648</v>
+        <v>666</v>
       </c>
       <c r="E73" s="43" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="F73" s="44"/>
     </row>
@@ -10615,19 +10711,19 @@
         <v>3</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="C74" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D74" s="42" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="E74" s="43" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="F74" s="44" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10635,19 +10731,19 @@
         <v>4</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="C75" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D75" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E75" s="43" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="F75" s="44" t="s">
-        <v>655</v>
+        <v>673</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10655,19 +10751,19 @@
         <v>5</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="C76" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D76" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E76" s="43" t="s">
-        <v>657</v>
+        <v>675</v>
       </c>
       <c r="F76" s="44" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10675,16 +10771,16 @@
         <v>6</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="C77" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D77" s="42" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
       <c r="E77" s="43" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="F77" s="44"/>
     </row>
@@ -10693,16 +10789,16 @@
         <v>7</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="C78" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D78" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E78" s="43" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="F78" s="44"/>
     </row>
@@ -10711,16 +10807,16 @@
         <v>8</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C79" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D79" s="42" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E79" s="43" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="F79" s="44"/>
     </row>
@@ -10729,16 +10825,16 @@
         <v>9</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C80" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D80" s="42" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="E80" s="43" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="F80" s="44"/>
     </row>
@@ -10747,16 +10843,16 @@
         <v>10</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="C81" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D81" s="42" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="E81" s="43" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="F81" s="44"/>
     </row>
@@ -10765,16 +10861,16 @@
         <v>11</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="C82" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D82" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E82" s="43" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="F82" s="44"/>
     </row>
@@ -10783,16 +10879,16 @@
         <v>12</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="C83" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D83" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E83" s="43" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="F83" s="44"/>
     </row>
@@ -10801,16 +10897,16 @@
         <v>13</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="C84" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D84" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E84" s="43" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="F84" s="44"/>
     </row>
@@ -10819,16 +10915,16 @@
         <v>14</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C85" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D85" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E85" s="43" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="F85" s="44"/>
     </row>
@@ -10837,16 +10933,16 @@
         <v>15</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C86" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D86" s="42" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="E86" s="43" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="F86" s="44"/>
     </row>
@@ -10855,19 +10951,19 @@
         <v>16</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="C87" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D87" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E87" s="43" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="F87" s="44" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10875,23 +10971,23 @@
         <v>17</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C88" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D88" s="42" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="E88" s="43" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="F88" s="44"/>
     </row>
     <row r="89" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="90" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="39" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="B90" s="39"/>
       <c r="C90" s="39"/>
@@ -10901,7 +10997,7 @@
     </row>
     <row r="91" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B91" s="40" t="s">
         <v>45</v>
@@ -10910,13 +11006,13 @@
         <v>79</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E91" s="40" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F91" s="40" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10924,19 +11020,19 @@
         <v>1</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="C92" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D92" s="42" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="E92" s="43" t="s">
-        <v>681</v>
+        <v>699</v>
       </c>
       <c r="F92" s="44" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10944,19 +11040,19 @@
         <v>2</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="C93" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D93" s="42" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
       <c r="E93" s="43" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F93" s="44" t="s">
-        <v>685</v>
+        <v>703</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10964,19 +11060,19 @@
         <v>3</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="C94" s="45" t="s">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="D94" s="42" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="E94" s="43" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="F94" s="44" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10984,16 +11080,16 @@
         <v>4</v>
       </c>
       <c r="B95" s="13" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
       <c r="C95" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D95" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E95" s="43" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="F95" s="44"/>
     </row>
@@ -11002,13 +11098,13 @@
         <v>5</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="C96" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D96" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E96" s="43"/>
       <c r="F96" s="44"/>
@@ -11018,19 +11114,19 @@
         <v>6</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="C97" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D97" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E97" s="43" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F97" s="44" t="s">
-        <v>695</v>
+        <v>713</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11038,16 +11134,16 @@
         <v>7</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>696</v>
+        <v>714</v>
       </c>
       <c r="C98" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D98" s="42" t="s">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="E98" s="43" t="s">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="F98" s="44"/>
     </row>
@@ -11056,16 +11152,16 @@
         <v>8</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="C99" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D99" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E99" s="43" t="s">
-        <v>699</v>
+        <v>717</v>
       </c>
       <c r="F99" s="44"/>
     </row>
@@ -11074,16 +11170,16 @@
         <v>9</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C100" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D100" s="42" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="E100" s="43" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="F100" s="44"/>
     </row>
@@ -11092,13 +11188,13 @@
         <v>10</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="C101" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D101" s="42" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E101" s="43"/>
       <c r="F101" s="44"/>
@@ -11108,19 +11204,19 @@
         <v>11</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="C102" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D102" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E102" s="43" t="s">
-        <v>703</v>
+        <v>721</v>
       </c>
       <c r="F102" s="44" t="s">
-        <v>704</v>
+        <v>722</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11128,16 +11224,16 @@
         <v>12</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="C103" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D103" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E103" s="43" t="s">
-        <v>706</v>
+        <v>724</v>
       </c>
       <c r="F103" s="44"/>
     </row>
@@ -11146,16 +11242,16 @@
         <v>13</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>707</v>
+        <v>725</v>
       </c>
       <c r="C104" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D104" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E104" s="43" t="s">
-        <v>708</v>
+        <v>726</v>
       </c>
       <c r="F104" s="44"/>
     </row>
@@ -11164,16 +11260,16 @@
         <v>14</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C105" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D105" s="42" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="E105" s="43" t="s">
-        <v>709</v>
+        <v>727</v>
       </c>
       <c r="F105" s="44"/>
     </row>
@@ -11182,19 +11278,19 @@
         <v>15</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C106" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D106" s="42" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="E106" s="43" t="s">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="F106" s="44" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11202,16 +11298,16 @@
         <v>16</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="C107" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D107" s="42" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="E107" s="43" t="s">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="F107" s="44"/>
     </row>
@@ -11220,23 +11316,23 @@
         <v>17</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="C108" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D108" s="42" t="s">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="E108" s="43" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="F108" s="44"/>
     </row>
     <row r="109" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="110" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="39" t="s">
-        <v>719</v>
+        <v>737</v>
       </c>
       <c r="B110" s="39"/>
       <c r="C110" s="39"/>
@@ -11246,7 +11342,7 @@
     </row>
     <row r="111" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B111" s="40" t="s">
         <v>45</v>
@@ -11255,13 +11351,13 @@
         <v>79</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E111" s="40" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F111" s="40" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11269,19 +11365,19 @@
         <v>1</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>720</v>
+        <v>738</v>
       </c>
       <c r="C112" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D112" s="42" t="s">
-        <v>721</v>
+        <v>739</v>
       </c>
       <c r="E112" s="43" t="s">
-        <v>722</v>
+        <v>740</v>
       </c>
       <c r="F112" s="44" t="s">
-        <v>723</v>
+        <v>741</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11289,19 +11385,19 @@
         <v>2</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="C113" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D113" s="42" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="E113" s="43" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
       <c r="F113" s="44" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11309,19 +11405,19 @@
         <v>3</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="C114" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D114" s="42" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="E114" s="43" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="F114" s="44" t="s">
-        <v>729</v>
+        <v>747</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11329,19 +11425,19 @@
         <v>4</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>730</v>
+        <v>748</v>
       </c>
       <c r="C115" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D115" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E115" s="43" t="s">
-        <v>731</v>
+        <v>749</v>
       </c>
       <c r="F115" s="44" t="s">
-        <v>732</v>
+        <v>750</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11349,16 +11445,16 @@
         <v>5</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>733</v>
+        <v>751</v>
       </c>
       <c r="C116" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D116" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E116" s="43" t="s">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="F116" s="44"/>
     </row>
@@ -11367,16 +11463,16 @@
         <v>6</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="C117" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D117" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E117" s="43" t="s">
-        <v>735</v>
+        <v>753</v>
       </c>
       <c r="F117" s="44"/>
     </row>
@@ -11385,16 +11481,16 @@
         <v>7</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="C118" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D118" s="42" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E118" s="43" t="s">
-        <v>736</v>
+        <v>754</v>
       </c>
       <c r="F118" s="44"/>
     </row>
@@ -11403,16 +11499,16 @@
         <v>8</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C119" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D119" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E119" s="43" t="s">
-        <v>737</v>
+        <v>755</v>
       </c>
       <c r="F119" s="44"/>
     </row>
@@ -11421,16 +11517,16 @@
         <v>9</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="C120" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D120" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E120" s="43" t="s">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="F120" s="44"/>
     </row>
@@ -11439,16 +11535,16 @@
         <v>10</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="C121" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D121" s="42" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E121" s="43" t="s">
-        <v>740</v>
+        <v>758</v>
       </c>
       <c r="F121" s="44"/>
     </row>
@@ -11457,19 +11553,19 @@
         <v>11</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="C122" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E122" s="43" t="s">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="F122" s="44" t="s">
-        <v>743</v>
+        <v>761</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11477,19 +11573,19 @@
         <v>12</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="C123" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="E123" s="43" t="s">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="F123" s="44" t="s">
-        <v>747</v>
+        <v>765</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11497,19 +11593,19 @@
         <v>13</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="C124" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D124" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E124" s="43" t="s">
-        <v>748</v>
+        <v>766</v>
       </c>
       <c r="F124" s="44" t="s">
-        <v>749</v>
+        <v>767</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11517,19 +11613,19 @@
         <v>14</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>750</v>
+        <v>768</v>
       </c>
       <c r="C125" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D125" s="42" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="E125" s="43" t="s">
-        <v>751</v>
+        <v>769</v>
       </c>
       <c r="F125" s="44" t="s">
-        <v>752</v>
+        <v>770</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11537,19 +11633,19 @@
         <v>15</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="C126" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D126" s="42" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="E126" s="43" t="s">
-        <v>754</v>
+        <v>772</v>
       </c>
       <c r="F126" s="44" t="s">
-        <v>755</v>
+        <v>773</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11557,23 +11653,23 @@
         <v>16</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="C127" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D127" s="42" t="s">
-        <v>757</v>
+        <v>775</v>
       </c>
       <c r="E127" s="43" t="s">
-        <v>758</v>
+        <v>776</v>
       </c>
       <c r="F127" s="44"/>
     </row>
     <row r="128" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="129" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="39" t="s">
-        <v>759</v>
+        <v>777</v>
       </c>
       <c r="B129" s="39"/>
       <c r="C129" s="39"/>
@@ -11583,7 +11679,7 @@
     </row>
     <row r="130" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B130" s="40" t="s">
         <v>45</v>
@@ -11592,13 +11688,13 @@
         <v>79</v>
       </c>
       <c r="D130" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E130" s="40" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F130" s="40" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11606,16 +11702,16 @@
         <v>1</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>760</v>
+        <v>778</v>
       </c>
       <c r="C131" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D131" s="42" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="E131" s="43" t="s">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="F131" s="44"/>
     </row>
@@ -11624,19 +11720,19 @@
         <v>2</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="C132" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D132" s="42" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="E132" s="43" t="s">
-        <v>762</v>
+        <v>780</v>
       </c>
       <c r="F132" s="44" t="s">
-        <v>763</v>
+        <v>781</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11644,19 +11740,19 @@
         <v>3</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>764</v>
+        <v>782</v>
       </c>
       <c r="C133" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D133" s="42" t="s">
-        <v>648</v>
+        <v>666</v>
       </c>
       <c r="E133" s="43" t="s">
-        <v>765</v>
+        <v>783</v>
       </c>
       <c r="F133" s="44" t="s">
-        <v>766</v>
+        <v>784</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11664,16 +11760,16 @@
         <v>4</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>767</v>
+        <v>785</v>
       </c>
       <c r="C134" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D134" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E134" s="43" t="s">
-        <v>768</v>
+        <v>786</v>
       </c>
       <c r="F134" s="44"/>
     </row>
@@ -11682,13 +11778,13 @@
         <v>5</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
       <c r="C135" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D135" s="42" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="E135" s="43"/>
       <c r="F135" s="44"/>
@@ -11698,19 +11794,19 @@
         <v>6</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>770</v>
+        <v>788</v>
       </c>
       <c r="C136" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D136" s="42" t="s">
-        <v>771</v>
+        <v>789</v>
       </c>
       <c r="E136" s="43" t="s">
-        <v>772</v>
+        <v>790</v>
       </c>
       <c r="F136" s="44" t="s">
-        <v>773</v>
+        <v>791</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11718,19 +11814,19 @@
         <v>7</v>
       </c>
       <c r="B137" s="13" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="C137" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D137" s="42" t="s">
-        <v>775</v>
+        <v>793</v>
       </c>
       <c r="E137" s="43" t="s">
-        <v>776</v>
+        <v>794</v>
       </c>
       <c r="F137" s="44" t="s">
-        <v>777</v>
+        <v>795</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11738,16 +11834,16 @@
         <v>8</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>778</v>
+        <v>796</v>
       </c>
       <c r="C138" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D138" s="42" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="E138" s="43" t="s">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="F138" s="44"/>
     </row>
@@ -11756,16 +11852,16 @@
         <v>9</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="C139" s="42" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D139" s="42" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E139" s="43" t="s">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="F139" s="44"/>
     </row>
@@ -11774,16 +11870,16 @@
         <v>10</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>782</v>
+        <v>800</v>
       </c>
       <c r="C140" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D140" s="42" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="E140" s="43" t="s">
-        <v>783</v>
+        <v>801</v>
       </c>
       <c r="F140" s="44"/>
     </row>
@@ -11792,16 +11888,16 @@
         <v>11</v>
       </c>
       <c r="B141" s="13" t="s">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="C141" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D141" s="42" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="E141" s="43" t="s">
-        <v>785</v>
+        <v>803</v>
       </c>
       <c r="F141" s="44"/>
     </row>
@@ -11810,16 +11906,16 @@
         <v>12</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="C142" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D142" s="42" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E142" s="43" t="s">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="F142" s="44"/>
     </row>
@@ -11828,16 +11924,16 @@
         <v>13</v>
       </c>
       <c r="B143" s="13" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="C143" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D143" s="42" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="E143" s="43" t="s">
-        <v>789</v>
+        <v>807</v>
       </c>
       <c r="F143" s="44"/>
     </row>
@@ -11846,19 +11942,19 @@
         <v>14</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="C144" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D144" s="42" t="s">
-        <v>757</v>
+        <v>775</v>
       </c>
       <c r="E144" s="43" t="s">
-        <v>790</v>
+        <v>808</v>
       </c>
       <c r="F144" s="44" t="s">
-        <v>791</v>
+        <v>809</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11866,16 +11962,16 @@
         <v>15</v>
       </c>
       <c r="B145" s="13" t="s">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="C145" s="41" t="s">
         <v>79</v>
       </c>
       <c r="D145" s="42" t="s">
-        <v>793</v>
+        <v>811</v>
       </c>
       <c r="E145" s="43" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="F145" s="44"/>
     </row>
@@ -11921,7 +12017,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>795</v>
+        <v>813</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11933,7 +12029,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>796</v>
+        <v>814</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11945,25 +12041,25 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>797</v>
+        <v>815</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>798</v>
+        <v>816</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>799</v>
+        <v>817</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>800</v>
+        <v>818</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>801</v>
+        <v>819</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>83</v>
@@ -11971,506 +12067,506 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>804</v>
+        <v>822</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>806</v>
+        <v>824</v>
       </c>
       <c r="E4" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="44" t="s">
-        <v>808</v>
+        <v>826</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="46" t="s">
-        <v>809</v>
+        <v>827</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>810</v>
+        <v>828</v>
       </c>
       <c r="E5" s="46" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="44"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="46" t="s">
-        <v>811</v>
+        <v>829</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>812</v>
+        <v>830</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>813</v>
+        <v>831</v>
       </c>
       <c r="E6" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="44"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="46" t="s">
-        <v>814</v>
+        <v>832</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>815</v>
+        <v>833</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>816</v>
+        <v>834</v>
       </c>
       <c r="E7" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="44"/>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="46" t="s">
-        <v>817</v>
+        <v>835</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E8" s="46" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="44"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="46" t="s">
-        <v>818</v>
+        <v>836</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="E9" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="44"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="E10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="44" t="s">
-        <v>823</v>
+        <v>841</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="46" t="s">
-        <v>824</v>
+        <v>842</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>825</v>
+        <v>843</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>826</v>
+        <v>844</v>
       </c>
       <c r="E11" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="44" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="46" t="s">
-        <v>828</v>
+        <v>846</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>829</v>
+        <v>847</v>
       </c>
       <c r="E12" s="46" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="44" t="s">
-        <v>830</v>
+        <v>848</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="46" t="s">
-        <v>831</v>
+        <v>849</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>832</v>
+        <v>850</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>833</v>
+        <v>851</v>
       </c>
       <c r="E13" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="44" t="s">
-        <v>834</v>
+        <v>852</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="46" t="s">
-        <v>835</v>
+        <v>853</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>836</v>
+        <v>854</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>837</v>
+        <v>855</v>
       </c>
       <c r="E14" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="44"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="46" t="s">
-        <v>838</v>
+        <v>856</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>840</v>
+        <v>858</v>
       </c>
       <c r="E15" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="44"/>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="46" t="s">
-        <v>841</v>
+        <v>859</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>843</v>
+        <v>861</v>
       </c>
       <c r="E16" s="46" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="44" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="46" t="s">
-        <v>845</v>
+        <v>863</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>846</v>
+        <v>864</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="E17" s="46" t="n">
         <v>4</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G17" s="16"/>
       <c r="H17" s="44"/>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="46" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="E18" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G18" s="16"/>
       <c r="H18" s="44"/>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>851</v>
+        <v>869</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>852</v>
+        <v>870</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>853</v>
+        <v>871</v>
       </c>
       <c r="E19" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="44" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="46" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>856</v>
+        <v>874</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>857</v>
+        <v>875</v>
       </c>
       <c r="E20" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="44"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="46" t="s">
-        <v>858</v>
+        <v>876</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>859</v>
+        <v>877</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>860</v>
+        <v>878</v>
       </c>
       <c r="E21" s="46" t="n">
         <v>3</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="44"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="46" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>862</v>
+        <v>880</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>863</v>
+        <v>881</v>
       </c>
       <c r="E22" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="44" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="46" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>867</v>
+        <v>885</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>868</v>
+        <v>886</v>
       </c>
       <c r="E23" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="44" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="46" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>872</v>
+        <v>890</v>
       </c>
       <c r="E24" s="46" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="44"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="46" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>874</v>
+        <v>892</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>875</v>
+        <v>893</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>876</v>
+        <v>894</v>
       </c>
       <c r="E25" s="46" t="n">
         <v>5</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="44" t="s">
-        <v>877</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -12526,451 +12622,451 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>878</v>
+        <v>896</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>881</v>
+        <v>899</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>883</v>
+        <v>901</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>889</v>
+        <v>907</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="B8" s="43" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>894</v>
+        <v>912</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>897</v>
+        <v>915</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>898</v>
+        <v>916</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>899</v>
+        <v>917</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>900</v>
+        <v>918</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>901</v>
+        <v>919</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>902</v>
+        <v>920</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>903</v>
+        <v>921</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>905</v>
+        <v>923</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="B18" s="43" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="B19" s="43" t="s">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="C19" s="43" t="s">
-        <v>918</v>
+        <v>936</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
       <c r="B20" s="43" t="s">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="C20" s="43" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="B21" s="43" t="s">
-        <v>923</v>
+        <v>941</v>
       </c>
       <c r="C21" s="43" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="39" t="s">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="B23" s="39"/>
       <c r="C23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="40" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>928</v>
+        <v>946</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>930</v>
+        <v>948</v>
       </c>
       <c r="C25" s="43" t="s">
-        <v>931</v>
+        <v>949</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>932</v>
+        <v>950</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>933</v>
+        <v>951</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>934</v>
+        <v>952</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>935</v>
+        <v>953</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>936</v>
+        <v>954</v>
       </c>
       <c r="C27" s="43" t="s">
-        <v>937</v>
+        <v>955</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>938</v>
+        <v>956</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>939</v>
+        <v>957</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>940</v>
+        <v>958</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>943</v>
+        <v>961</v>
       </c>
       <c r="B30" s="43" t="s">
-        <v>944</v>
+        <v>962</v>
       </c>
       <c r="C30" s="43" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="39" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="B32" s="39"/>
       <c r="C32" s="39"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="40" t="s">
-        <v>947</v>
+        <v>965</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>948</v>
+        <v>966</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>949</v>
+        <v>967</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>950</v>
+        <v>968</v>
       </c>
       <c r="B34" s="43" t="s">
-        <v>951</v>
+        <v>969</v>
       </c>
       <c r="C34" s="43" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>953</v>
+        <v>971</v>
       </c>
       <c r="B35" s="43" t="s">
-        <v>954</v>
+        <v>972</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>955</v>
+        <v>973</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>956</v>
+        <v>974</v>
       </c>
       <c r="B36" s="43" t="s">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="C36" s="43" t="s">
-        <v>958</v>
+        <v>976</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="B37" s="43" t="s">
-        <v>960</v>
+        <v>978</v>
       </c>
       <c r="C37" s="43" t="s">
-        <v>961</v>
+        <v>979</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>962</v>
+        <v>980</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>963</v>
+        <v>981</v>
       </c>
       <c r="C38" s="43" t="s">
-        <v>964</v>
+        <v>982</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="39" t="s">
-        <v>965</v>
+        <v>983</v>
       </c>
       <c r="B40" s="39"/>
       <c r="C40" s="39"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="40" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>966</v>
+        <v>984</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>967</v>
+        <v>985</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>968</v>
+        <v>986</v>
       </c>
       <c r="C42" s="43" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="B43" s="43" t="s">
-        <v>970</v>
+        <v>988</v>
       </c>
       <c r="C43" s="43" t="s">
-        <v>971</v>
+        <v>989</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="B44" s="43" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="C44" s="43" t="s">
-        <v>973</v>
+        <v>991</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="B45" s="43" t="s">
-        <v>974</v>
+        <v>992</v>
       </c>
       <c r="C45" s="43" t="s">
-        <v>975</v>
+        <v>993</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="B46" s="43" t="s">
-        <v>976</v>
+        <v>994</v>
       </c>
       <c r="C46" s="43" t="s">
-        <v>977</v>
+        <v>995</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
       <c r="B47" s="43" t="s">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="C47" s="43" t="s">
-        <v>979</v>
+        <v>997</v>
       </c>
     </row>
   </sheetData>
@@ -13014,7 +13110,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>980</v>
+        <v>998</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13028,35 +13124,35 @@
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="47" t="s">
-        <v>981</v>
+        <v>999</v>
       </c>
       <c r="B2" s="48" t="n">
         <f aca="false">COUNTA(A4:A24)</f>
         <v>21</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>982</v>
+        <v>1000</v>
       </c>
       <c r="D2" s="48" t="n">
         <f aca="false">COUNTIF(D4:D24,"已上架")</f>
         <v>0</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>983</v>
+        <v>1001</v>
       </c>
       <c r="F2" s="48" t="n">
         <f aca="false">COUNTIF(D4:D24,"审核中")</f>
         <v>0</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="H2" s="48" t="n">
         <f aca="false">COUNTIF(D4:D24,"被驳回")</f>
         <v>0</v>
       </c>
       <c r="I2" s="47" t="s">
-        <v>985</v>
+        <v>1003</v>
       </c>
       <c r="J2" s="49" t="n">
         <f aca="false">IF(OR(B2="",B2=0),"",D2/B2)</f>
@@ -13065,31 +13161,31 @@
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>986</v>
+        <v>1004</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>988</v>
+        <v>1006</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>989</v>
+        <v>1007</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>990</v>
+        <v>1008</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>991</v>
+        <v>1009</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>994</v>
+        <v>1012</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>83</v>
@@ -13097,16 +13193,16 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="50" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E4" s="53"/>
       <c r="F4" s="54"/>
@@ -13117,16 +13213,16 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="50" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E5" s="53"/>
       <c r="F5" s="54"/>
@@ -13137,16 +13233,16 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="50" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E6" s="53"/>
       <c r="F6" s="54"/>
@@ -13157,16 +13253,16 @@
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="50" t="s">
-        <v>999</v>
+        <v>1017</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="54"/>
@@ -13177,16 +13273,16 @@
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="50" t="s">
-        <v>999</v>
+        <v>1017</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E8" s="53"/>
       <c r="F8" s="54"/>
@@ -13197,16 +13293,16 @@
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="50" t="s">
-        <v>999</v>
+        <v>1017</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E9" s="53"/>
       <c r="F9" s="54"/>
@@ -13223,10 +13319,10 @@
         <v>87</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E10" s="53"/>
       <c r="F10" s="54"/>
@@ -13243,10 +13339,10 @@
         <v>87</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E11" s="53"/>
       <c r="F11" s="54"/>
@@ -13263,10 +13359,10 @@
         <v>87</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E12" s="53"/>
       <c r="F12" s="54"/>
@@ -13283,10 +13379,10 @@
         <v>87</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E13" s="53"/>
       <c r="F13" s="54"/>
@@ -13303,10 +13399,10 @@
         <v>87</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E14" s="53"/>
       <c r="F14" s="54"/>
@@ -13323,10 +13419,10 @@
         <v>87</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E15" s="53"/>
       <c r="F15" s="54"/>
@@ -13343,10 +13439,10 @@
         <v>87</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E16" s="53"/>
       <c r="F16" s="54"/>
@@ -13363,10 +13459,10 @@
         <v>87</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E17" s="53"/>
       <c r="F17" s="54"/>
@@ -13383,10 +13479,10 @@
         <v>87</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E18" s="53"/>
       <c r="F18" s="54"/>
@@ -13403,10 +13499,10 @@
         <v>87</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E19" s="53"/>
       <c r="F19" s="54"/>
@@ -13423,10 +13519,10 @@
         <v>87</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E20" s="53"/>
       <c r="F20" s="54"/>
@@ -13443,10 +13539,10 @@
         <v>87</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E21" s="53"/>
       <c r="F21" s="54"/>
@@ -13463,10 +13559,10 @@
         <v>87</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E22" s="53"/>
       <c r="F22" s="54"/>
@@ -13483,10 +13579,10 @@
         <v>87</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E23" s="53"/>
       <c r="F23" s="54"/>
@@ -13503,10 +13599,10 @@
         <v>87</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>996</v>
+        <v>1014</v>
       </c>
       <c r="E24" s="53"/>
       <c r="F24" s="54"/>
